--- a/Regionalized FeliX/Model Files/Reg_InitialValues.xlsx
+++ b/Regionalized FeliX/Model Files/Reg_InitialValues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/Regionalied FeliX/Model Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/Regionalized FeliX/Model Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="411" documentId="13_ncr:1_{BC87DD94-8A18-4A38-BD52-67B37BD28289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84931982-18AA-4C02-A06E-A6A93D4B203D}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="695" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5856" yWindow="2472" windowWidth="17280" windowHeight="8880" tabRatio="695" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stocks" sheetId="1" r:id="rId1"/>
